--- a/training/sensor_roles.xlsx
+++ b/training/sensor_roles.xlsx
@@ -4782,7 +4782,7 @@
         <x:v>КА-1 Ток двигателя ВГД-1А</x:v>
       </x:c>
       <x:c r="B270" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C270" s="9" t="str">
         <x:v>ток двигателя вгд-#а</x:v>
@@ -4798,7 +4798,7 @@
         <x:v>КА-1 Ток двигателя ВГД-1Б</x:v>
       </x:c>
       <x:c r="B271" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C271" s="9" t="str">
         <x:v>ток двигателя вгд-#б</x:v>
@@ -4814,7 +4814,7 @@
         <x:v>КА-1 Ток двигателя ВГД-1В</x:v>
       </x:c>
       <x:c r="B272" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C272" s="9" t="str">
         <x:v>ток двигателя вгд-#в</x:v>
@@ -4830,7 +4830,7 @@
         <x:v>КА-1 Ток двигателя ВГД-1Г</x:v>
       </x:c>
       <x:c r="B273" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C273" s="9" t="str">
         <x:v>ток двигателя вгд-#г</x:v>
@@ -4846,7 +4846,7 @@
         <x:v>КА-1 Ток двигателя ДВ-1А</x:v>
       </x:c>
       <x:c r="B274" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C274" s="9" t="str">
         <x:v>ток двигателя дв-#а</x:v>
@@ -4862,7 +4862,7 @@
         <x:v>КА-1 Ток двигателя ДВ-1Б</x:v>
       </x:c>
       <x:c r="B275" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C275" s="9" t="str">
         <x:v>ток двигателя дв-#б</x:v>
@@ -4878,7 +4878,7 @@
         <x:v>КА-1 Ток двигателя ДС-1А</x:v>
       </x:c>
       <x:c r="B276" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C276" s="9" t="str">
         <x:v>ток двигателя дс-#а</x:v>
@@ -4894,7 +4894,7 @@
         <x:v>КА-1 Ток двигателя ДС-1Б</x:v>
       </x:c>
       <x:c r="B277" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C277" s="9" t="str">
         <x:v>ток двигателя дс-#б</x:v>
@@ -4910,7 +4910,7 @@
         <x:v>КА-1 Ток двигателя ММТ-1А</x:v>
       </x:c>
       <x:c r="B278" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C278" s="9" t="str">
         <x:v>ток двигателя ммт-#а</x:v>
@@ -4926,7 +4926,7 @@
         <x:v>КА-1 Ток двигателя ММТ-1Б</x:v>
       </x:c>
       <x:c r="B279" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C279" s="9" t="str">
         <x:v>ток двигателя ммт-#б</x:v>
@@ -4942,7 +4942,7 @@
         <x:v>КА-1 Ток двигателя ММТ-1В</x:v>
       </x:c>
       <x:c r="B280" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C280" s="9" t="str">
         <x:v>ток двигателя ммт-#в</x:v>
@@ -4958,7 +4958,7 @@
         <x:v>КА-1 Ток двигателя ММТ-1Г</x:v>
       </x:c>
       <x:c r="B281" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C281" s="9" t="str">
         <x:v>ток двигателя ммт-#г</x:v>
@@ -4974,7 +4974,7 @@
         <x:v>КА-1 Ток двигателя ПСУ 1Б</x:v>
       </x:c>
       <x:c r="B282" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C282" s="9" t="str">
         <x:v>ток двигателя псу-#б</x:v>
@@ -4990,7 +4990,7 @@
         <x:v>КА-1 Ток двигателя ПСУ 1В</x:v>
       </x:c>
       <x:c r="B283" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C283" s="9" t="str">
         <x:v>ток двигателя псу-#в</x:v>
@@ -5006,7 +5006,7 @@
         <x:v>КА-1 Ток двигателя ПСУ 1Г</x:v>
       </x:c>
       <x:c r="B284" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C284" s="9" t="str">
         <x:v>ток двигателя псу-#г</x:v>
@@ -5022,7 +5022,7 @@
         <x:v>КА-1 Ток двигателя ПСУ-1А</x:v>
       </x:c>
       <x:c r="B285" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C285" s="9" t="str">
         <x:v>ток двигателя псу-#а</x:v>
@@ -9149,7 +9149,7 @@
         <x:v>КА-2 Ток двигателя ВГД-2А</x:v>
       </x:c>
       <x:c r="B249" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C249" s="9" t="str">
         <x:v>ток двигателя вгд-#а</x:v>
@@ -9165,7 +9165,7 @@
         <x:v>КА-2 Ток двигателя ВГД-2Б</x:v>
       </x:c>
       <x:c r="B250" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C250" s="9" t="str">
         <x:v>ток двигателя вгд-#б</x:v>
@@ -9181,7 +9181,7 @@
         <x:v>КА-2 Ток двигателя ВГД-2В</x:v>
       </x:c>
       <x:c r="B251" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C251" s="9" t="str">
         <x:v>ток двигателя вгд-#в</x:v>
@@ -9197,7 +9197,7 @@
         <x:v>КА-2 Ток двигателя ВГД-2Г</x:v>
       </x:c>
       <x:c r="B252" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C252" s="9" t="str">
         <x:v>ток двигателя вгд-#г</x:v>
@@ -9213,7 +9213,7 @@
         <x:v>КА-2 Ток двигателя ДВ-2А</x:v>
       </x:c>
       <x:c r="B253" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C253" s="9" t="str">
         <x:v>ток двигателя дв-#а</x:v>
@@ -9229,7 +9229,7 @@
         <x:v>КА-2 Ток двигателя ДВ-2Б</x:v>
       </x:c>
       <x:c r="B254" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C254" s="9" t="str">
         <x:v>ток двигателя дв-#б</x:v>
@@ -9245,7 +9245,7 @@
         <x:v>КА-2 Ток двигателя ДС-2А</x:v>
       </x:c>
       <x:c r="B255" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C255" s="9" t="str">
         <x:v>ток двигателя дс-#а</x:v>
@@ -9261,7 +9261,7 @@
         <x:v>КА-2 Ток двигателя ДС-2Б</x:v>
       </x:c>
       <x:c r="B256" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C256" s="9" t="str">
         <x:v>ток двигателя дс-#б</x:v>
@@ -9277,7 +9277,7 @@
         <x:v>КА-2 Ток двигателя КОР-1А</x:v>
       </x:c>
       <x:c r="B257" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C257" s="9" t="str">
         <x:v>ток двигателя кор-1а</x:v>
@@ -9293,7 +9293,7 @@
         <x:v>КА-2 Ток двигателя КОР-1Б</x:v>
       </x:c>
       <x:c r="B258" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C258" s="9" t="str">
         <x:v>ток двигателя кор-1б</x:v>
@@ -9309,7 +9309,7 @@
         <x:v>КА-2 Ток двигателя КОР-2А</x:v>
       </x:c>
       <x:c r="B259" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C259" s="9" t="str">
         <x:v>ток двигателя кор-2а</x:v>
@@ -9325,7 +9325,7 @@
         <x:v>КА-2 Ток двигателя КОР-2Б</x:v>
       </x:c>
       <x:c r="B260" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C260" s="9" t="str">
         <x:v>ток двигателя кор-2б</x:v>
@@ -9341,7 +9341,7 @@
         <x:v>КА-2 Ток двигателя КОР-3А</x:v>
       </x:c>
       <x:c r="B261" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C261" s="9" t="str">
         <x:v>ток двигателя кор-3а</x:v>
@@ -9357,7 +9357,7 @@
         <x:v>КА-2 Ток двигателя КОР-3Б</x:v>
       </x:c>
       <x:c r="B262" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C262" s="9" t="str">
         <x:v>ток двигателя кор-3б</x:v>
@@ -9373,7 +9373,7 @@
         <x:v>КА-2 Ток двигателя КОР-4А</x:v>
       </x:c>
       <x:c r="B263" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C263" s="9" t="str">
         <x:v>ток двигателя кор-4а</x:v>
@@ -9389,7 +9389,7 @@
         <x:v>КА-2 Ток двигателя КОР-4Б</x:v>
       </x:c>
       <x:c r="B264" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C264" s="9" t="str">
         <x:v>ток двигателя кор-4б</x:v>
@@ -9405,7 +9405,7 @@
         <x:v>КА-2 Ток двигателя ММТ-2А</x:v>
       </x:c>
       <x:c r="B265" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C265" s="9" t="str">
         <x:v>ток двигателя ммт-#а</x:v>
@@ -9421,7 +9421,7 @@
         <x:v>КА-2 Ток двигателя ММТ-2Б</x:v>
       </x:c>
       <x:c r="B266" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C266" s="9" t="str">
         <x:v>ток двигателя ммт-#б</x:v>
@@ -9437,7 +9437,7 @@
         <x:v>КА-2 Ток двигателя ММТ-2В</x:v>
       </x:c>
       <x:c r="B267" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C267" s="9" t="str">
         <x:v>ток двигателя ммт-#в</x:v>
@@ -9453,7 +9453,7 @@
         <x:v>КА-2 Ток двигателя ММТ-2Г</x:v>
       </x:c>
       <x:c r="B268" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C268" s="9" t="str">
         <x:v>ток двигателя ммт-#г</x:v>
@@ -9469,7 +9469,7 @@
         <x:v>КА-2 Ток двигателя ОС-1А</x:v>
       </x:c>
       <x:c r="B269" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C269" s="9" t="str">
         <x:v>ток двигателя ос-1а</x:v>
@@ -9485,7 +9485,7 @@
         <x:v>КА-2 Ток двигателя ОС-1Б</x:v>
       </x:c>
       <x:c r="B270" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C270" s="9" t="str">
         <x:v>ток двигателя ос-1б</x:v>
@@ -9501,7 +9501,7 @@
         <x:v>КА-2 Ток двигателя ОС-2А</x:v>
       </x:c>
       <x:c r="B271" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C271" s="9" t="str">
         <x:v>ток двигателя ос-2а</x:v>
@@ -9517,7 +9517,7 @@
         <x:v>КА-2 Ток двигателя ОС-2Б</x:v>
       </x:c>
       <x:c r="B272" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C272" s="9" t="str">
         <x:v>ток двигателя ос-2б</x:v>
@@ -9533,7 +9533,7 @@
         <x:v>КА-2 Ток двигателя ОС-3А</x:v>
       </x:c>
       <x:c r="B273" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C273" s="9" t="str">
         <x:v>ток двигателя ос-3а</x:v>
@@ -9549,7 +9549,7 @@
         <x:v>КА-2 Ток двигателя ОС-3Б</x:v>
       </x:c>
       <x:c r="B274" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C274" s="9" t="str">
         <x:v>ток двигателя ос-3б</x:v>
@@ -9565,7 +9565,7 @@
         <x:v>КА-2 Ток двигателя ОС-4А</x:v>
       </x:c>
       <x:c r="B275" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C275" s="9" t="str">
         <x:v>ток двигателя ос-4а</x:v>
@@ -9581,7 +9581,7 @@
         <x:v>КА-2 Ток двигателя ОС-4Б</x:v>
       </x:c>
       <x:c r="B276" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C276" s="9" t="str">
         <x:v>ток двигателя ос-4б</x:v>
@@ -9597,7 +9597,7 @@
         <x:v>КА-2 Ток двигателя ПСУ 2Б</x:v>
       </x:c>
       <x:c r="B277" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C277" s="9" t="str">
         <x:v>ток двигателя псу-#б</x:v>
@@ -9613,7 +9613,7 @@
         <x:v>КА-2 Ток двигателя ПСУ 2В</x:v>
       </x:c>
       <x:c r="B278" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C278" s="9" t="str">
         <x:v>ток двигателя псу-#в</x:v>
@@ -9629,7 +9629,7 @@
         <x:v>КА-2 Ток двигателя ПСУ 2Г</x:v>
       </x:c>
       <x:c r="B279" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C279" s="9" t="str">
         <x:v>ток двигателя псу-#г</x:v>
@@ -9645,7 +9645,7 @@
         <x:v>КА-2 Ток двигателя ПСУ-2А</x:v>
       </x:c>
       <x:c r="B280" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C280" s="9" t="str">
         <x:v>ток двигателя псу-#а</x:v>
@@ -9661,7 +9661,7 @@
         <x:v>КА-2 Ток шнека А</x:v>
       </x:c>
       <x:c r="B281" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C281" s="9" t="str">
         <x:v>ток шнека а</x:v>
@@ -9677,7 +9677,7 @@
         <x:v>КА-2 Ток шнека Б</x:v>
       </x:c>
       <x:c r="B282" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C282" s="9" t="str">
         <x:v>ток шнека б</x:v>
@@ -9693,7 +9693,7 @@
         <x:v>КА-2 Ток шнека В</x:v>
       </x:c>
       <x:c r="B283" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C283" s="9" t="str">
         <x:v>ток шнека в</x:v>
@@ -9709,7 +9709,7 @@
         <x:v>КА-2 Ток шнека Г</x:v>
       </x:c>
       <x:c r="B284" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C284" s="9" t="str">
         <x:v>ток шнека г</x:v>
@@ -13088,7 +13088,7 @@
         <x:v>KA-3 Ток двигателя ДВ-3А</x:v>
       </x:c>
       <x:c r="B200" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C200" s="9" t="str">
         <x:v>ток двигателя дв-#а</x:v>
@@ -13104,7 +13104,7 @@
         <x:v>KA-3 Ток двигателя ДВ-3Б</x:v>
       </x:c>
       <x:c r="B201" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C201" s="9" t="str">
         <x:v>ток двигателя дв-#б</x:v>
@@ -13120,7 +13120,7 @@
         <x:v>KA-3 Ток двигателя ДС-3А</x:v>
       </x:c>
       <x:c r="B202" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C202" s="9" t="str">
         <x:v>ток двигателя дс-#а</x:v>
@@ -13136,7 +13136,7 @@
         <x:v>KA-3 Ток двигателя ДС-3Б</x:v>
       </x:c>
       <x:c r="B203" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C203" s="9" t="str">
         <x:v>ток двигателя дс-#б</x:v>
@@ -13152,7 +13152,7 @@
         <x:v>KA-3 Ток двигателя ММТ-3А</x:v>
       </x:c>
       <x:c r="B204" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C204" s="9" t="str">
         <x:v>ток двигателя ммт-#а</x:v>
@@ -13168,7 +13168,7 @@
         <x:v>KA-3 Ток двигателя ММТ-3Б</x:v>
       </x:c>
       <x:c r="B205" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C205" s="9" t="str">
         <x:v>ток двигателя ммт-#б</x:v>
@@ -13184,7 +13184,7 @@
         <x:v>KA-3 Ток двигателя ММТ-3В</x:v>
       </x:c>
       <x:c r="B206" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C206" s="9" t="str">
         <x:v>ток двигателя ммт-#в</x:v>
@@ -13200,7 +13200,7 @@
         <x:v>KA-3 Ток двигателя ММТ-3Г</x:v>
       </x:c>
       <x:c r="B207" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C207" s="9" t="str">
         <x:v>ток двигателя ммт-#г</x:v>
@@ -13216,7 +13216,7 @@
         <x:v>KA-3 Ток двигателя ПСУ 3Б</x:v>
       </x:c>
       <x:c r="B208" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C208" s="9" t="str">
         <x:v>ток двигателя псу-#б</x:v>
@@ -13232,7 +13232,7 @@
         <x:v>KA-3 Ток двигателя ПСУ 3В</x:v>
       </x:c>
       <x:c r="B209" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C209" s="9" t="str">
         <x:v>ток двигателя псу-#в</x:v>
@@ -13248,7 +13248,7 @@
         <x:v>KA-3 Ток двигателя ПСУ 3Г</x:v>
       </x:c>
       <x:c r="B210" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C210" s="9" t="str">
         <x:v>ток двигателя псу-#г</x:v>
@@ -13264,7 +13264,7 @@
         <x:v>KA-3 Ток двигателя ПСУ-3А</x:v>
       </x:c>
       <x:c r="B211" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C211" s="9" t="str">
         <x:v>ток двигателя псу-#а</x:v>
@@ -17125,7 +17125,7 @@
         <x:v>КА-4 Ток двигателя ДВ-4А</x:v>
       </x:c>
       <x:c r="B205" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C205" s="9" t="str">
         <x:v>ток двигателя дв-#а</x:v>
@@ -17141,7 +17141,7 @@
         <x:v>КА-4 Ток двигателя ДВ-4Б</x:v>
       </x:c>
       <x:c r="B206" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C206" s="9" t="str">
         <x:v>ток двигателя дв-#б</x:v>
@@ -17157,7 +17157,7 @@
         <x:v>КА-4 Ток двигателя ДС-4А</x:v>
       </x:c>
       <x:c r="B207" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C207" s="9" t="str">
         <x:v>ток двигателя дс-#а</x:v>
@@ -17173,7 +17173,7 @@
         <x:v>КА-4 Ток двигателя ДС-4Б</x:v>
       </x:c>
       <x:c r="B208" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C208" s="9" t="str">
         <x:v>ток двигателя дс-#б</x:v>
@@ -17189,7 +17189,7 @@
         <x:v>КА-4 Ток двигателя ММТ-4А</x:v>
       </x:c>
       <x:c r="B209" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C209" s="9" t="str">
         <x:v>ток двигателя ммт-#а</x:v>
@@ -17205,7 +17205,7 @@
         <x:v>КА-4 Ток двигателя ММТ-4Б</x:v>
       </x:c>
       <x:c r="B210" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C210" s="9" t="str">
         <x:v>ток двигателя ммт-#б</x:v>
@@ -17221,7 +17221,7 @@
         <x:v>КА-4 Ток двигателя ММТ-4В</x:v>
       </x:c>
       <x:c r="B211" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C211" s="9" t="str">
         <x:v>ток двигателя ммт-#в</x:v>
@@ -17237,7 +17237,7 @@
         <x:v>КА-4 Ток двигателя ММТ-4Г</x:v>
       </x:c>
       <x:c r="B212" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C212" s="9" t="str">
         <x:v>ток двигателя ммт-#г</x:v>
@@ -17253,7 +17253,7 @@
         <x:v>КА-4 Ток двигателя ПСУ 4Б</x:v>
       </x:c>
       <x:c r="B213" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C213" s="9" t="str">
         <x:v>ток двигателя псу-#б</x:v>
@@ -17269,7 +17269,7 @@
         <x:v>КА-4 Ток двигателя ПСУ 4В</x:v>
       </x:c>
       <x:c r="B214" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C214" s="9" t="str">
         <x:v>ток двигателя псу-#в</x:v>
@@ -17285,7 +17285,7 @@
         <x:v>КА-4 Ток двигателя ПСУ 4Г</x:v>
       </x:c>
       <x:c r="B215" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C215" s="9" t="str">
         <x:v>ток двигателя псу-#г</x:v>
@@ -17301,7 +17301,7 @@
         <x:v>КА-4 Ток двигателя ПСУ-4А</x:v>
       </x:c>
       <x:c r="B216" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C216" s="9" t="str">
         <x:v>ток двигателя псу-#а</x:v>
@@ -19592,7 +19592,7 @@
         <x:v>КА-5 Выходной ток на управление ПСУ-5А</x:v>
       </x:c>
       <x:c r="B135" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C135" s="9" t="str">
         <x:v>выходной ток на управление псу-#а</x:v>
@@ -19608,7 +19608,7 @@
         <x:v>КА-5 Выходной ток на управление ПСУ-5Б</x:v>
       </x:c>
       <x:c r="B136" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C136" s="9" t="str">
         <x:v>выходной ток на управление псу-#б</x:v>
@@ -19624,7 +19624,7 @@
         <x:v>КА-5 Выходной ток на управление ПСУ-5В</x:v>
       </x:c>
       <x:c r="B137" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C137" s="9" t="str">
         <x:v>выходной ток на управление псу-#в</x:v>
@@ -19640,7 +19640,7 @@
         <x:v>КА-5 Выходной ток на управление ПСУ-5Г</x:v>
       </x:c>
       <x:c r="B138" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C138" s="9" t="str">
         <x:v>выходной ток на управление псу-#г</x:v>
@@ -21020,7 +21020,7 @@
         <x:v>КА-5 Ток двигателя ДВ-5А</x:v>
       </x:c>
       <x:c r="B224" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C224" s="9" t="str">
         <x:v>ток двигателя дв-#а</x:v>
@@ -21036,7 +21036,7 @@
         <x:v>КА-5 Ток двигателя ДВ-5Б</x:v>
       </x:c>
       <x:c r="B225" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C225" s="9" t="str">
         <x:v>ток двигателя дв-#б</x:v>
@@ -21052,7 +21052,7 @@
         <x:v>КА-5 Ток двигателя ДРГ-5А</x:v>
       </x:c>
       <x:c r="B226" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C226" s="9" t="str">
         <x:v>ток двигателя дрг-#а</x:v>
@@ -21068,7 +21068,7 @@
         <x:v>КА-5 Ток двигателя ДРГ-5Б</x:v>
       </x:c>
       <x:c r="B227" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C227" s="9" t="str">
         <x:v>ток двигателя дрг-#б</x:v>
@@ -21084,7 +21084,7 @@
         <x:v>КА-5 Ток двигателя ДС-5А</x:v>
       </x:c>
       <x:c r="B228" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C228" s="9" t="str">
         <x:v>ток двигателя дс-#а</x:v>
@@ -21100,7 +21100,7 @@
         <x:v>КА-5 Ток двигателя ДС-5Б</x:v>
       </x:c>
       <x:c r="B229" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C229" s="9" t="str">
         <x:v>ток двигателя дс-#б</x:v>
@@ -21116,7 +21116,7 @@
         <x:v>КА-5 Ток двигателя МВ-5А</x:v>
       </x:c>
       <x:c r="B230" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C230" s="9" t="str">
         <x:v>ток двигателя мв-#а</x:v>
@@ -21132,7 +21132,7 @@
         <x:v>КА-5 Ток двигателя МВ-5Б</x:v>
       </x:c>
       <x:c r="B231" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C231" s="9" t="str">
         <x:v>ток двигателя мв-#б</x:v>
@@ -21148,7 +21148,7 @@
         <x:v>КА-5 Ток двигателя МВ-5В</x:v>
       </x:c>
       <x:c r="B232" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C232" s="9" t="str">
         <x:v>ток двигателя мв-#в</x:v>
@@ -21164,7 +21164,7 @@
         <x:v>КА-5 Ток двигателя МВ-5Г</x:v>
       </x:c>
       <x:c r="B233" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C233" s="9" t="str">
         <x:v>ток двигателя мв-#г</x:v>
@@ -21180,7 +21180,7 @@
         <x:v>КА-5 Ток двигателя ПСУ-5А</x:v>
       </x:c>
       <x:c r="B234" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C234" s="9" t="str">
         <x:v>ток двигателя псу-#а</x:v>
@@ -21196,7 +21196,7 @@
         <x:v>КА-5 Ток двигателя ПСУ-5Б</x:v>
       </x:c>
       <x:c r="B235" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C235" s="9" t="str">
         <x:v>ток двигателя псу-#б</x:v>
@@ -21212,7 +21212,7 @@
         <x:v>КА-5 Ток двигателя ПСУ-5В</x:v>
       </x:c>
       <x:c r="B236" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C236" s="9" t="str">
         <x:v>ток двигателя псу-#в</x:v>
@@ -21228,7 +21228,7 @@
         <x:v>КА-5 Ток двигателя ПСУ-5Г</x:v>
       </x:c>
       <x:c r="B237" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C237" s="9" t="str">
         <x:v>ток двигателя псу-#г</x:v>
@@ -23323,7 +23323,7 @@
         <x:v>KA-6 Выходной ток на управление ПСУ-6А</x:v>
       </x:c>
       <x:c r="B121" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C121" s="9" t="str">
         <x:v>выходной ток на управление псу-#а</x:v>
@@ -23339,7 +23339,7 @@
         <x:v>KA-6 Выходной ток на управление ПСУ-6Б</x:v>
       </x:c>
       <x:c r="B122" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C122" s="9" t="str">
         <x:v>выходной ток на управление псу-#б</x:v>
@@ -23355,7 +23355,7 @@
         <x:v>KA-6 Выходной ток на управление ПСУ-6В</x:v>
       </x:c>
       <x:c r="B123" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C123" s="9" t="str">
         <x:v>выходной ток на управление псу-#в</x:v>
@@ -23371,7 +23371,7 @@
         <x:v>KA-6 Выходной ток на управление ПСУ-6Г</x:v>
       </x:c>
       <x:c r="B124" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C124" s="9" t="str">
         <x:v>выходной ток на управление псу-#г</x:v>
@@ -24239,7 +24239,7 @@
         <x:v>KA-6 Ток двигателя ДВ-6А</x:v>
       </x:c>
       <x:c r="B178" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C178" s="9" t="str">
         <x:v>ток двигателя дв-#а</x:v>
@@ -24255,7 +24255,7 @@
         <x:v>KA-6 Ток двигателя ДВ-6Б</x:v>
       </x:c>
       <x:c r="B179" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C179" s="9" t="str">
         <x:v>ток двигателя дв-#б</x:v>
@@ -24271,7 +24271,7 @@
         <x:v>KA-6 Ток двигателя ДРГ-6А</x:v>
       </x:c>
       <x:c r="B180" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C180" s="9" t="str">
         <x:v>ток двигателя дрг-#а</x:v>
@@ -24287,7 +24287,7 @@
         <x:v>KA-6 Ток двигателя ДРГ-6Б</x:v>
       </x:c>
       <x:c r="B181" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C181" s="9" t="str">
         <x:v>ток двигателя дрг-#б</x:v>
@@ -24303,7 +24303,7 @@
         <x:v>KA-6 Ток двигателя ДС-6А</x:v>
       </x:c>
       <x:c r="B182" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C182" s="9" t="str">
         <x:v>ток двигателя дс-#а</x:v>
@@ -24319,7 +24319,7 @@
         <x:v>KA-6 Ток двигателя ДС-6Б</x:v>
       </x:c>
       <x:c r="B183" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C183" s="9" t="str">
         <x:v>ток двигателя дс-#б</x:v>
@@ -24335,7 +24335,7 @@
         <x:v>KA-6 Ток двигателя МВ-6А</x:v>
       </x:c>
       <x:c r="B184" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C184" s="9" t="str">
         <x:v>ток двигателя мв-#а</x:v>
@@ -24351,7 +24351,7 @@
         <x:v>KA-6 Ток двигателя МВ-6Б</x:v>
       </x:c>
       <x:c r="B185" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C185" s="9" t="str">
         <x:v>ток двигателя мв-#б</x:v>
@@ -24367,7 +24367,7 @@
         <x:v>KA-6 Ток двигателя МВ-6В</x:v>
       </x:c>
       <x:c r="B186" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C186" s="9" t="str">
         <x:v>ток двигателя мв-#в</x:v>
@@ -24383,7 +24383,7 @@
         <x:v>KA-6 Ток двигателя МВ-6Г</x:v>
       </x:c>
       <x:c r="B187" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C187" s="9" t="str">
         <x:v>ток двигателя мв-#г</x:v>
@@ -24399,7 +24399,7 @@
         <x:v>KA-6 Ток двигателя ПСУ-6А</x:v>
       </x:c>
       <x:c r="B188" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C188" s="9" t="str">
         <x:v>ток двигателя псу-#а</x:v>
@@ -24415,7 +24415,7 @@
         <x:v>KA-6 Ток двигателя ПСУ-6Б</x:v>
       </x:c>
       <x:c r="B189" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C189" s="9" t="str">
         <x:v>ток двигателя псу-#б</x:v>
@@ -24431,7 +24431,7 @@
         <x:v>KA-6 Ток двигателя ПСУ-6В</x:v>
       </x:c>
       <x:c r="B190" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C190" s="9" t="str">
         <x:v>ток двигателя псу-#в</x:v>
@@ -24447,7 +24447,7 @@
         <x:v>KA-6 Ток двигателя ПСУ-6Г</x:v>
       </x:c>
       <x:c r="B191" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C191" s="9" t="str">
         <x:v>ток двигателя псу-#г</x:v>
@@ -26898,7 +26898,7 @@
         <x:v>KA-7 Выходной ток на управление ПСУ-7А</x:v>
       </x:c>
       <x:c r="B124" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C124" s="9" t="str">
         <x:v>выходной ток на управление псу-#а</x:v>
@@ -26914,7 +26914,7 @@
         <x:v>KA-7 Выходной ток на управление ПСУ-7Б</x:v>
       </x:c>
       <x:c r="B125" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C125" s="9" t="str">
         <x:v>выходной ток на управление псу-#б</x:v>
@@ -26930,7 +26930,7 @@
         <x:v>KA-7 Выходной ток на управление ПСУ-7В</x:v>
       </x:c>
       <x:c r="B126" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C126" s="9" t="str">
         <x:v>выходной ток на управление псу-#в</x:v>
@@ -26946,7 +26946,7 @@
         <x:v>KA-7 Выходной ток на управление ПСУ-7Г</x:v>
       </x:c>
       <x:c r="B127" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C127" s="9" t="str">
         <x:v>выходной ток на управление псу-#г</x:v>
@@ -27894,7 +27894,7 @@
         <x:v>KA-7 Ток двигателя ДВ-7А</x:v>
       </x:c>
       <x:c r="B186" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C186" s="9" t="str">
         <x:v>ток двигателя дв-#а</x:v>
@@ -27910,7 +27910,7 @@
         <x:v>KA-7 Ток двигателя ДВ-7Б</x:v>
       </x:c>
       <x:c r="B187" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C187" s="9" t="str">
         <x:v>ток двигателя дв-#б</x:v>
@@ -27926,7 +27926,7 @@
         <x:v>KA-7 Ток двигателя ДРГ-7А</x:v>
       </x:c>
       <x:c r="B188" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C188" s="9" t="str">
         <x:v>ток двигателя дрг-#а</x:v>
@@ -27942,7 +27942,7 @@
         <x:v>KA-7 Ток двигателя ДРГ-7Б</x:v>
       </x:c>
       <x:c r="B189" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C189" s="9" t="str">
         <x:v>ток двигателя дрг-#б</x:v>
@@ -27958,7 +27958,7 @@
         <x:v>KA-7 Ток двигателя ДС-7А</x:v>
       </x:c>
       <x:c r="B190" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C190" s="9" t="str">
         <x:v>ток двигателя дс-#а</x:v>
@@ -27974,7 +27974,7 @@
         <x:v>KA-7 Ток двигателя ДС-7Б</x:v>
       </x:c>
       <x:c r="B191" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C191" s="9" t="str">
         <x:v>ток двигателя дс-#б</x:v>
@@ -27990,7 +27990,7 @@
         <x:v>KA-7 Ток двигателя МВ-7А</x:v>
       </x:c>
       <x:c r="B192" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C192" s="9" t="str">
         <x:v>ток двигателя мв-#а</x:v>
@@ -28006,7 +28006,7 @@
         <x:v>KA-7 Ток двигателя МВ-7Б</x:v>
       </x:c>
       <x:c r="B193" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C193" s="9" t="str">
         <x:v>ток двигателя мв-#б</x:v>
@@ -28022,7 +28022,7 @@
         <x:v>KA-7 Ток двигателя МВ-7В</x:v>
       </x:c>
       <x:c r="B194" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C194" s="9" t="str">
         <x:v>ток двигателя мв-#в</x:v>
@@ -28038,7 +28038,7 @@
         <x:v>KA-7 Ток двигателя МВ-7Г</x:v>
       </x:c>
       <x:c r="B195" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C195" s="9" t="str">
         <x:v>ток двигателя мв-#г</x:v>
@@ -28054,7 +28054,7 @@
         <x:v>KA-7 Ток двигателя ПСУ-7А</x:v>
       </x:c>
       <x:c r="B196" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C196" s="9" t="str">
         <x:v>ток двигателя псу-#а</x:v>
@@ -28070,7 +28070,7 @@
         <x:v>KA-7 Ток двигателя ПСУ-7Б</x:v>
       </x:c>
       <x:c r="B197" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C197" s="9" t="str">
         <x:v>ток двигателя псу-#б</x:v>
@@ -28086,7 +28086,7 @@
         <x:v>KA-7 Ток двигателя ПСУ-7В</x:v>
       </x:c>
       <x:c r="B198" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C198" s="9" t="str">
         <x:v>ток двигателя псу-#в</x:v>
@@ -28102,7 +28102,7 @@
         <x:v>KA-7 Ток двигателя ПСУ-7Г</x:v>
       </x:c>
       <x:c r="B199" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C199" s="9" t="str">
         <x:v>ток двигателя псу-#г</x:v>
@@ -31245,7 +31245,7 @@
         <x:v>KA-8 Ток двигателя ДВ-8А</x:v>
       </x:c>
       <x:c r="B180" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C180" s="9" t="str">
         <x:v>ток двигателя дв-#а</x:v>
@@ -31261,7 +31261,7 @@
         <x:v>KA-8 Ток двигателя ДВ-8Б</x:v>
       </x:c>
       <x:c r="B181" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C181" s="9" t="str">
         <x:v>ток двигателя дв-#б</x:v>
@@ -31277,7 +31277,7 @@
         <x:v>KA-8 Ток двигателя ДРГ-8А</x:v>
       </x:c>
       <x:c r="B182" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C182" s="9" t="str">
         <x:v>ток двигателя дрг-#а</x:v>
@@ -31293,7 +31293,7 @@
         <x:v>KA-8 Ток двигателя ДРГ-8Б</x:v>
       </x:c>
       <x:c r="B183" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C183" s="9" t="str">
         <x:v>ток двигателя дрг-#б</x:v>
@@ -31309,7 +31309,7 @@
         <x:v>KA-8 Ток двигателя ДС-8А</x:v>
       </x:c>
       <x:c r="B184" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C184" s="9" t="str">
         <x:v>ток двигателя дс-#а</x:v>
@@ -31325,7 +31325,7 @@
         <x:v>KA-8 Ток двигателя ДС-8Б</x:v>
       </x:c>
       <x:c r="B185" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C185" s="9" t="str">
         <x:v>ток двигателя дс-#б</x:v>
@@ -31341,7 +31341,7 @@
         <x:v>KA-8 Ток двигателя МВ-8А</x:v>
       </x:c>
       <x:c r="B186" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C186" s="9" t="str">
         <x:v>ток двигателя мв-#а</x:v>
@@ -31357,7 +31357,7 @@
         <x:v>KA-8 Ток двигателя МВ-8Б</x:v>
       </x:c>
       <x:c r="B187" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C187" s="9" t="str">
         <x:v>ток двигателя мв-#б</x:v>
@@ -31373,7 +31373,7 @@
         <x:v>KA-8 Ток двигателя МВ-8В</x:v>
       </x:c>
       <x:c r="B188" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C188" s="9" t="str">
         <x:v>ток двигателя мв-#в</x:v>
@@ -31389,7 +31389,7 @@
         <x:v>KA-8 Ток двигателя МВ-8Г</x:v>
       </x:c>
       <x:c r="B189" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C189" s="9" t="str">
         <x:v>ток двигателя мв-#г</x:v>
@@ -31405,7 +31405,7 @@
         <x:v>KA-8 Ток двигателя МВ-8Д</x:v>
       </x:c>
       <x:c r="B190" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C190" s="9" t="str">
         <x:v>ток двигателя мв-#д</x:v>
@@ -31421,7 +31421,7 @@
         <x:v>KA-8 Ток двигателя МВ-8Е</x:v>
       </x:c>
       <x:c r="B191" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C191" s="9" t="str">
         <x:v>ток двигателя мв-#е</x:v>
@@ -31437,7 +31437,7 @@
         <x:v>KA-8 Ток двигателя ПСУ-8А</x:v>
       </x:c>
       <x:c r="B192" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C192" s="9" t="str">
         <x:v>ток двигателя псу-#а</x:v>
@@ -31453,7 +31453,7 @@
         <x:v>KA-8 Ток двигателя ПСУ-8Б</x:v>
       </x:c>
       <x:c r="B193" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C193" s="9" t="str">
         <x:v>ток двигателя псу-#б</x:v>
@@ -31469,7 +31469,7 @@
         <x:v>KA-8 Ток двигателя ПСУ-8В</x:v>
       </x:c>
       <x:c r="B194" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C194" s="9" t="str">
         <x:v>ток двигателя псу-#в</x:v>
@@ -31485,7 +31485,7 @@
         <x:v>KA-8 Ток двигателя ПСУ-8Г</x:v>
       </x:c>
       <x:c r="B195" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C195" s="9" t="str">
         <x:v>ток двигателя псу-#г</x:v>
@@ -31501,7 +31501,7 @@
         <x:v>KA-8 Ток двигателя ПСУ-8Д</x:v>
       </x:c>
       <x:c r="B196" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C196" s="9" t="str">
         <x:v>ток двигателя псу-#д</x:v>
@@ -31517,7 +31517,7 @@
         <x:v>KA-8 Ток двигателя ПСУ-8Е</x:v>
       </x:c>
       <x:c r="B197" s="8" t="str">
-        <x:v>проверять</x:v>
+        <x:v>условие</x:v>
       </x:c>
       <x:c r="C197" s="9" t="str">
         <x:v>ток двигателя псу-#е</x:v>
